--- a/docs/herramientas-mx/contenedores.xlsx
+++ b/docs/herramientas-mx/contenedores.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Comparativo_8450" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="No_caben" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Fuentes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cambios_sesion_nocturna" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -587,7 +588,7 @@
         <v>22.7</v>
       </c>
       <c r="M2" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -596,7 +597,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>milwaukeetool.com / Home Depot MX (snippet): 'barra de seguridad de bloqueo... cerrar los cajones con candado'</t>
+          <t>CAT pag. 10 "Locking security bar" + MLK features</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -606,7 +607,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>ext D2 · CAT pag. 10 + MLK Length/Width/Height; HDUS 16.3 x 22.2 x 14.3 in</t>
         </is>
       </c>
     </row>
@@ -657,6 +658,9 @@
       <c r="L3" t="n">
         <v>22.7</v>
       </c>
+      <c r="M3" t="n">
+        <v>10.18</v>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>si</t>
@@ -664,7 +668,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Home Depot MX / milwaukeetool.com (snippet)</t>
+          <t>CAT pag. 11 + MLK features</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -674,7 +678,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>ext D2 · CAT pag. 11 + MLK; HDUS 16.3 x 22.2 x 14.3; HDMX 40.89 x 36.2 cm (fondo x alto)</t>
         </is>
       </c>
     </row>
@@ -713,18 +717,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>61, 61, 130</t>
+          <t>63, 63, 127</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>33.8</v>
+        <v>33.3</v>
       </c>
       <c r="K4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="L4" t="n">
         <v>22.7</v>
       </c>
+      <c r="M4" t="n">
+        <v>10.66</v>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>si</t>
@@ -732,7 +739,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>milwaukeetool.com (snippet): 'locking security bar that allows you to padlock the drawers closed'</t>
+          <t>MLK features "Locking Security Bar"</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -742,7 +749,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>ext D2 · MLK; HDUS 16.10 x 22.2 x 14.3 in</t>
         </is>
       </c>
     </row>
@@ -781,18 +788,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61, 61, 61, 61</t>
+          <t>58, 58, 58, 58</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>32.7</v>
+        <v>30.5</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>8.41</v>
       </c>
       <c r="L5" t="n">
         <v>22.7</v>
       </c>
+      <c r="M5" t="n">
+        <v>10.89</v>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>si</t>
@@ -800,17 +810,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>milwaukeetool.com (snippet)</t>
+          <t>MLK features "Locking Security Bar"; HDUS preguntas: la barra se guarda bajo la caja</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4 juegos de divisores Quick-Adjust. Cajones bajos (61 mm útiles).</t>
+          <t>El cajon es de 58 mm, NO de 61 mm (fragmento UK de la sesion anterior). La imagen oficial rotula 22.2 in como "54.4 cm": error de la imagen, 22.2 in = 56.4 cm. 4 juegos de divisores Quick-Adjust. Cajones bajos (61 mm útiles).</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>ext D2 · MLK Length 16.3 / Width 22.2 / Height 14.3 in; HDUS 16.10 x 22.2 x 14.3 in (5 mm menos de fondo)</t>
         </is>
       </c>
     </row>
@@ -842,15 +852,28 @@
         <v>564</v>
       </c>
       <c r="G6" t="n">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.1</v>
+      </c>
       <c r="L6" t="n">
         <v>22.7</v>
       </c>
+      <c r="M6" t="n">
+        <v>10.5</v>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>si</t>
@@ -858,7 +881,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>redtoolstore (título, snippet): 'with Locking Bar and Dividers'</t>
+          <t>MLK features "Locking Security Bar"</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -868,7 +891,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>ext D1 · MLK imagen: 22.2 x 16.3 x 14 in; MLK especificaciones Height 14.3; HDUS 22 x 22.5 x 14.5 in</t>
         </is>
       </c>
     </row>
@@ -894,10 +917,10 @@
         </is>
       </c>
       <c r="E7" t="n">
+        <v>483</v>
+      </c>
+      <c r="F7" t="n">
         <v>610</v>
-      </c>
-      <c r="F7" t="n">
-        <v>483</v>
       </c>
       <c r="G7" t="n">
         <v>502</v>
@@ -920,26 +943,26 @@
         <v>113.4</v>
       </c>
       <c r="M7" t="n">
-        <v>13.2</v>
+        <v>13.15</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>sin dato</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>no encontrado</t>
+          <t>MLK no lista "Locking Security Bar" (si la lista en 8441/8442/8443/8444/8447). Comprador en HDUS: "hay que desapilar todo lo que va encima para poder ponerle candado".</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Candidata directa como BASE del carrito: rueda, acepta PACKOUT encima (stack &amp; lock) y aporta un cajón profundo de 16 in. Incluye 2 divisores grandes, 6 chicos y bandeja removible (ToolGuyd).</t>
+          <t>Incluye 2 divisores grandes, 6 divisores y una bandeja interior (MLK "Includes"). Peso: MLK 29 lb, HDUS 36 lb. Candidata directa como BASE del carrito: rueda, acepta PACKOUT encima (stack &amp; lock) y aporta un cajón profundo de 16 in. Incluye 2 divisores grandes, 6 chicos y bandeja removible (ToolGuyd).</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>ext D2 · MLK imagen: 24 x 19 x 19.75 in; MLK especificaciones 24 x 19 x 20 in; HDUS 23.9 x 19.49 x 19.82 in</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1412,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>int: snippet de búsqueda sobre Zoro/US (https://www.zoro.com/milwaukee-tool-packout-2-drawer-tool-box-50-lb-capacity-25-lb-capacity-per-drawer-22-w-x-16-d-x-14-h-48-22-8442/i/G300719715/); 25 lb/cajón en título Zoro. Ver notas: fuente UK da 61/130 mm (contradictoria).</t>
+          <t>CAT pag. 10 (imagen): cajon 16.3 x 12.5 in, 5 in de alto; https://www.milwaukeetool.com/products/48-22-8442</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1447,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>int_mm: distribuidores UK modelo 4932472130 (snippet): '76 x 414 x 318 mm (inner)', 11 kg/cajón; una fuente dice 127 x 414 x 318</t>
+          <t>CAT pag. 11 (imagen): cajon 16.3 x 12.5 in, 3 in de alto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1443,28 +1466,28 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D4" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>11</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>distribuidores UK modelo 4932493190 '2+1 Drawer' (snippet): 'small drawers 61 x 416 x 322 mm'; equivalencia 4932493190 = 48-22-8447 es INFERENCIA</t>
+          <t>MLK imagen "48-22-8447 Dimensions": 2 cajones de 2.5 in (6.35 cm)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1478,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D5" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
         <v>11</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>idem: 'large drawer 130 x 416 x 322 mm'</t>
+          <t>MLK imagen "48-22-8447 Dimensions": 1 cajon de 5 in (12.7 cm)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1513,28 +1536,28 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D6" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
         <v>11</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>UK modelo 4932493189 (CEF / electricalwholesaler, snippet): 'inner dimensions 61 x 416 x 322 mm', 11 kg/cajón</t>
+          <t>MLK imagen "48-22-8444 Dimensions": cajon 16.3 x 12.5 in, 2.3 in (5.8 cm) de alto; respuesta de comprador en HDUS repite 2.3 x 16.3 x 12.5 in tomado de la misma imagen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1547,14 +1570,29 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
+      <c r="C7" t="n">
+        <v>419</v>
+      </c>
+      <c r="D7" t="n">
+        <v>330</v>
+      </c>
+      <c r="E7" t="n">
+        <v>260</v>
+      </c>
+      <c r="F7" t="n">
+        <v>250</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22.7</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>no encontrado</t>
+          <t>MLK imagen "48-22-8441 Dimensions 101": cajon 16.5 x 13 in (41.9 x 33 cm), 10.25 in (26 cm)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1622,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ToolGuyd (snippet): 'Interior Dimensions: 17 L x 13 D x 16 H' — la capacidad 250 lb es del conjunto, no se publica por cajón</t>
+          <t>MLK imagen "48-22-8420 Dimensions 101": 13 in de ancho de cajon y 16 in de alto; el tercer lado (432 mm) sigue siendo fragmento de buscador</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>no validado (fragmento de buscador; falta ficha oficial y vernier)</t>
+          <t>D1 (13 y 16 in) / D1 fragmento (432)</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1613,6 +1651,8 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1646,6 +1686,16 @@
           <t>confianza</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>precio_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1676,6 +1726,11 @@
           <t>baja: snippet</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1701,6 +1756,11 @@
           <t>baja: snippet</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1728,6 +1788,11 @@
           <t>listado existe; precio no visible en snippet, sitio bloqueado</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1755,20 +1820,22 @@
           <t>listado existe; precio no visible</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>48-22-8443</t>
+          <t>48-22-8442</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Home Depot MX</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3399</v>
+          <t>The Home Depot EUA (referencia, USD)</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1777,13 +1844,21 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramientas-packout-de-3-cajones-milwaukee-48-22-8443-165831</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-2-Drawer-Tool-Box-with-Metal-Reinforced-Corners-48-22-8442/315059770</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>media: snippet de buscador, no página abierta</t>
-        </is>
+          <t>referencia de precio de lista EUA, sin impuestos</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -1794,11 +1869,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>milwaukeestore.com.mx</t>
+          <t>The Home Depot Mexico (pagina leida)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4889</v>
+        <v>3799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1807,28 +1882,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://milwaukeestore.com.mx/products/caja-de-herramientas-de-3-cajones-packout%E2%84%A2-48-22-8443</t>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramientas-packout-de-3-cajones-milwaukee-48-22-8443-165831</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>media: snippet</t>
+          <t>alta: pagina abierta</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>incluido</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>48-22-8447</t>
+          <t>48-22-8443</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no atribuible con certeza (probable Mercado Libre MX)</t>
+          <t>Home Depot MX</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4787</v>
+        <v>3399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1837,28 +1917,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.mx/caja-herramienta-3-cajones-difs-packout-48228447-milwaukee/p/MLM38060933</t>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramientas-packout-de-3-cajones-milwaukee-48-22-8443-165831</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>baja: snippet</t>
+          <t>media: snippet de buscador, no página abierta</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>48-22-8444</t>
+          <t>48-22-8443</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mercado Libre MX</t>
+          <t>milwaukeestore.com.mx</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4799</v>
+        <v>4889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1867,24 +1952,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.mx/caja-de-herramientas-4-cajones-packout-48228444-milwaukee/p/MLM38396653</t>
+          <t>https://milwaukeestore.com.mx/products/caja-de-herramientas-de-3-cajones-packout%E2%84%A2-48-22-8443</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>media-baja: snippet</t>
+          <t>media: snippet</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>48-22-8444</t>
+          <t>48-22-8443</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ferrecsa / Micra Herramientas / Amazon MX</t>
+          <t>The Home Depot EUA (referencia, USD)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1894,28 +1984,36 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://ferrecsa.com.mx/Producto/caja-packout-4-cajones-48-22-8444-milwaukee</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-Modular-3-Drawer-Tool-Box-with-Metal-Reinforced-Corners-48-22-8443/315059793</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>listado existe; sin precio visible</t>
-        </is>
+          <t>referencia de precio de lista EUA, sin impuestos</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no atribuible (Mercado Libre MX / herramientaelectrica.mx)</t>
+          <t>no atribuible con certeza (probable Mercado Libre MX)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5999</v>
+        <v>4787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1924,28 +2022,30 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.mercadolibre.com.mx/caja-con-ruedas-cajon-delantero-packout-milwaukee-48-22-8420-rojo/p/MLM60702351</t>
+          <t>https://www.mercadolibre.com.mx/caja-herramienta-3-cajones-difs-packout-48228447-milwaukee/p/MLM38060933</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>baja: snippet</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no atribuible</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5599</v>
+          <t>The Home Depot EUA (referencia, USD)</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,53 +2054,68 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://herramientaelectrica.mx/products/caja-de-herramientas-con-cajones-y-ruedas-packout-48-22-8420</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-Modular-3-Drawer-Multi-Drawer-Tool-Box-with-Metal-Reinforced-Corners-and-50-lbs-Capacity-48-22-8447/326479354</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>baja</t>
-        </is>
+          <t>referencia de precio de lista EUA, sin impuestos</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no atribuible (oferta, antes 7,581)</t>
+          <t>Mercado Libre MX</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6799</v>
+        <v>4799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.mercadolibre.com.mx/caja-de-herramientas-4-cajones-packout-48228444-milwaukee/p/MLM38396653</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>media-baja: snippet</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>48-22-8426</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Home Depot MX (Pro)</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3815</v>
+          <t>Ferrecsa / Micra Herramientas / Amazon MX</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,28 +2124,30 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://pro.homedepot.com.mx/pro/herramientas/cajas-para-herramientas-y-organizadores/organizadores/caja-con-ruedas-packout-milwauke-139086</t>
+          <t>https://ferrecsa.com.mx/Producto/caja-packout-4-cajones-48-22-8444-milwaukee</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>media: snippet ('antes $4,239')</t>
+          <t>listado existe; sin precio visible</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sin dato</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>48-22-8410</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ferreterías Calzada</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2345</v>
+          <t>The Home Depot EUA (referencia, USD)</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,24 +2156,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://ferreteriacalzada.mx/producto/paquete-dolly-250lbs-modulo-almac-milwaukee-48-22-8410/</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-Modular-4-Drawer-Tool-Box-with-Metal-Reinforced-Corners-and-50-lbs-Capacity-48-22-8444/326480385</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>media-baja: snippet ('con IVA')</t>
-        </is>
+          <t>referencia de precio de lista EUA, sin impuestos</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>48-22-8450</t>
+          <t>48-22-8441</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Home Depot MX</t>
+          <t>The Home Depot EUA (referencia, USD)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2066,222 +2191,572 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-almacenamiento-packout-con-inserto-1501-x-38-x-529-cm-milwaukee-48-22-8450-139212</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-Single-Drawer-Tool-Box-48-22-8441/342729532</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>listado existe (SKU 139212); precio no visible</t>
-        </is>
+          <t>referencia de precio de lista EUA, sin impuestos</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>164</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48-22-8447</t>
+          <t>48-22-8420</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P05566)</t>
+          <t>no atribuible (Mercado Libre MX / herramientaelectrica.mx)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3499</v>
+        <v>5999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odoo purchase.order P05566</t>
+          <t>https://www.mercadolibre.com.mx/caja-con-ruedas-cajon-delantero-packout-milwaukee-48-22-8420-rojo/p/MLM60702351</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pagado por FTS, sin IVA</t>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>48-22-8444 (probable)</t>
+          <t>48-22-8420</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P03220)</t>
+          <t>no atribuible</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3614</v>
+        <v>5599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odoo purchase.order P03220</t>
+          <t>https://herramientaelectrica.mx/products/caja-de-herramientas-con-cajones-y-ruedas-packout-48-22-8420</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pagado por FTS, sin IVA; descripcion "CAJA DE HERRAMIENTAS CON 4 CAJONES PACKOUT"</t>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>48-22-8427</t>
+          <t>48-22-8420</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P05566)</t>
+          <t>no atribuible (oferta, antes 7,581)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2825</v>
+        <v>6799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Odoo purchase.order P05566</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pagado por FTS, sin IVA</t>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>incluido (precio de tienda MX)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>48-22-8450</t>
+          <t>48-22-8420</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Home Depot Mexico (Odoo P01829/P02096/P02097/P02102)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1854.4</v>
+          <t>The Home Depot EUA (referencia, USD)</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Odoo</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-19-in-Rolling-Drawer-Tool-Box-48-22-8420/334615696</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>pagado por FTS, sin IVA; el listado dice $1,565</t>
-        </is>
+          <t>referencia de precio de lista EUA, sin impuestos</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>48-22-8424</t>
+          <t>48-22-8426</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Home Depot Mexico (Odoo P01829)</t>
+          <t>The Home Depot Mexico (pagina leida)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1465.78</v>
+        <v>3799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odoo</t>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramienta-packout-con-llantas-67-x-49-x-4724-cm-milwaukee-48-22-8426-139086</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>pagado por FTS, sin IVA</t>
+          <t>alta: pagina abierta</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>incluido</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>48-22-8440</t>
+          <t>48-22-8426</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P02408)</t>
+          <t>Home Depot MX (Pro)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1089</v>
+        <v>3815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Odoo</t>
+          <t>https://pro.homedepot.com.mx/pro/herramientas/cajas-para-herramientas-y-organizadores/organizadores/caja-con-ruedas-packout-milwauke-139086</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>pagado por FTS, sin IVA</t>
+          <t>media: snippet ('antes $4,239')</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>sin dato</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>48-22-8410</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ferreterías Calzada</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2345</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://ferreteriacalzada.mx/producto/paquete-dolly-250lbs-modulo-almac-milwaukee-48-22-8410/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>media-baja: snippet ('con IVA')</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>48-22-8450</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Home Depot Mexico (pagina leida)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2159</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-almacenamiento-packout-con-inserto-1501-x-38-x-529-cm-milwaukee-48-22-8450-139212</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>alta: pagina abierta</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>48-22-8450</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Home Depot MX</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-almacenamiento-packout-con-inserto-1501-x-38-x-529-cm-milwaukee-48-22-8450-139212</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>listado existe (SKU 139212); precio no visible</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P05566)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3499</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Odoo purchase.order P05566</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>pagado por FTS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>sin IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>48-22-8444 (probable)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P03220)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3614</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Odoo purchase.order P03220</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pagado por FTS; descripcion "CAJA DE HERRAMIENTAS CON 4 CAJONES PACKOUT"</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>sin IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>48-22-8427</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P05566)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2825</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Odoo purchase.order P05566</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>pagado por FTS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>sin IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>48-22-8450</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Home Depot Mexico (Odoo P01829/P02096/P02097/P02102)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1854.4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Odoo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>pagado por FTS; el listado dice $1,565</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>sin IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>48-22-8424</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Home Depot Mexico (Odoo P01829)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1465.78</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Odoo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pagado por FTS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>sin IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>48-22-8440</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P02408)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1089</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Odoo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>pagado por FTS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>sin IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>48-22-8485</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>CENTRO DE HERRAMIENTAS Y SERVICIOS (Odoo P02408)</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C32" t="n">
         <v>589</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Odoo</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>placa de montaje, sin IVA</t>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>placa de montaje</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>sin IVA</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2421,17 +2896,17 @@
         <v>363</v>
       </c>
       <c r="C5" t="n">
-        <v>33.8</v>
+        <v>33.3</v>
       </c>
       <c r="D5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="E5" t="n">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 cajones de 61, 61, 130 mm</t>
+          <t>3 cajones de 63, 63, 127 mm</t>
         </is>
       </c>
     </row>
@@ -2445,39 +2920,63 @@
         <v>363</v>
       </c>
       <c r="C6" t="n">
-        <v>32.7</v>
+        <v>30.5</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8.41</v>
       </c>
       <c r="E6" t="n">
-        <v>22.9</v>
+        <v>28</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4 cajones de 61, 61, 61, 61 mm</t>
+          <t>4 cajones de 58, 58, 58, 58 mm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>48-22-8441</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>356</v>
+      </c>
+      <c r="C7" t="n">
+        <v>36</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1 cajones de 260 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>48-22-8420 (base con ruedas)</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>502</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>57.9</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>11.53</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>1.2</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1 cajon profundo; ruedas y manija ocupan altura</t>
         </is>
@@ -2661,7 +3160,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>406 (8420 base)</t>
+          <t>260 (8441), 406 (8420 base)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2703,12 +3202,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>406 (8420 base)</t>
+          <t>260 (8441), 406 (8420 base)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>largo 668 mm &gt; 416 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
+          <t>largo 668 mm &gt; 414 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2745,12 +3244,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>61 (8444, 8447 chicos), 76 (8443), 127 (8442), 130 (8447 hondo), 406 (8420 base)</t>
+          <t>58 (8444), 63 (8447 chicos), 76 (8443), 127 (8442, 8447 hondo), 260 (8441), 406 (8420 base)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>largo 630 mm &gt; 416 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
+          <t>largo 630 mm &gt; 414 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2792,7 +3291,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>largo 434 mm &gt; 416 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
+          <t>largo 434 mm &gt; 414 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2826,7 +3325,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>406 (8420 base)</t>
+          <t>260 (8441), 406 (8420 base)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2868,12 +3367,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>406 (8420 base)</t>
+          <t>260 (8441), 406 (8420 base)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>largo 533 mm &gt; 416 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
+          <t>largo 533 mm &gt; 414 mm de ancho de cajon (cabria en diagonal solo si &lt; 520)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2893,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2944,22 +3443,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ext_in</t>
+          <t>cajones</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22.2 W x 16.3 L x 14.3 H in</t>
+          <t>CAT pag. 10 (imagen): cajon 16.3 x 12.5 in, 5 in de alto; https://www.milwaukeetool.com/products/48-22-8442</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.northerntool.com/products/milwaukee-packout-2-drawer-tool-box-16-3in-l-x-22-2in-w-x-14-3in-h-model-48-22-8442-103364</t>
+          <t>https://www.milwaukeetool.com/-/media/PDFs/Sizing-Charts/PACKOUT-2023-Dimension-Catalog.pdf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tienda (US) - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante (leido hoy, pagina completa)</t>
         </is>
       </c>
     </row>
@@ -2971,22 +3470,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ext_in (alterno)</t>
+          <t>ext</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22.2 x 16.2 x 14.3 in</t>
+          <t>CAT pag. 10 + MLK Length/Width/Height; HDUS 16.3 x 22.2 x 14.3 in</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/clp/B08189NW5C</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-2-Drawer-Tool-Box-with-Metal-Reinforced-Corners-48-22-8442/315059770</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tienda (Amazon US) - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante + distribuidor EUA</t>
         </is>
       </c>
     </row>
@@ -2998,22 +3497,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ext_mm (UK 4932472129)</t>
+          <t>ext_in</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>564 x 414 x 363 mm</t>
+          <t>22.2 W x 16.3 L x 14.3 H in</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.powertoolworld.co.uk/milwaukee-packout-2-drawer-tool-box-4932472129</t>
+          <t>https://www.northerntool.com/products/milwaukee-packout-2-drawer-tool-box-16-3in-l-x-22-2in-w-x-14-3in-h-model-48-22-8442-103364</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda (US) - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
@@ -3025,22 +3524,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ext_cm (MX)</t>
+          <t>ext_in (alterno)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38 x 42 x 57 cm, 10 kg</t>
+          <t>22.2 x 16.2 x 14.3 in</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.ferrepat.com/herramientas-manuales/caja-para-herramienta-milwaukee-14299</t>
+          <t>https://www.amazon.com/clp/B08189NW5C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda (Amazon US) - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
@@ -3052,22 +3551,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>peso_vacio</t>
+          <t>ext_mm (UK 4932472129)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20.05 lb</t>
+          <t>564 x 414 x 363 mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.toolnut.com/milwaukee-48-22-8442-packout-2-drawer-tool-box.html</t>
+          <t>https://www.powertoolworld.co.uk/milwaukee-packout-2-drawer-tool-box-4932472129</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress) (atribución del buscador incierta)</t>
+          <t>(sesion anterior) distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
@@ -3079,22 +3578,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>capacidad_total</t>
+          <t>ext_cm (MX)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50 lb (US) / 22.5 kg (UK)</t>
+          <t>38 x 42 x 57 cm, 10 kg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.milwaukeetool.com/products/details/packout-2-drawer-tool-box/48-22-8442</t>
+          <t>https://www.ferrepat.com/herramientas-manuales/caja-para-herramienta-milwaukee-14299</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>oficial Milwaukee - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
@@ -3106,22 +3605,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>capacidad_por_cajon</t>
+          <t>peso_vacio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11 kg por cajón (UK); 25 lb por cajón (Zoro)</t>
+          <t>20.05 lb</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.sgs-engineering.com/milwaukee-4932472129-packouttm-2-drawer-tool-box</t>
+          <t>https://www.toolnut.com/milwaukee-48-22-8442-packout-2-drawer-tool-box.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress) (atribución del buscador incierta)</t>
         </is>
       </c>
     </row>
@@ -3133,76 +3632,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>int (UK, contradictorio)</t>
+          <t>capacidad_total</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cajón chico 61x416x322 mm, grande 130x416x322 mm</t>
+          <t>50 lb (US) / 22.5 kg (UK)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://imilwauke.pl/en/25303-4932472129-packout-2-drawer-tool-box-560-x-410-x-360-mm.html</t>
+          <t>https://www.milwaukeetool.com/products/details/packout-2-drawer-tool-box/48-22-8442</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>distribuidor PL - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) oficial Milwaukee - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>48-22-8443</t>
+          <t>48-22-8442</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ext_in</t>
+          <t>capacidad_por_cajon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16.3 L x 22.2 W x 14.3 H in</t>
+          <t>11 kg por cajón (UK); 25 lb por cajón (Zoro)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.northerntool.com/products/milwaukee-packout-3-drawer-tool-box-16-3in-l-x-22-2in-w-x-14-3in-h-model-48-22-8443-103365</t>
+          <t>https://www.sgs-engineering.com/milwaukee-4932472129-packouttm-2-drawer-tool-box</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>48-22-8443</t>
+          <t>48-22-8442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ext_mm (UK 4932472130)</t>
+          <t>int (UK, contradictorio)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>363 x 564 x 414 mm; peso 10 kg; capacidad 22 kg</t>
+          <t>cajón chico 61x416x322 mm, grande 130x416x322 mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.electricalwholesaler.ie/en/products/milwaukee-packout-3-drawer-tool-box-4932472130</t>
+          <t>https://imilwauke.pl/en/25303-4932472129-packout-2-drawer-tool-box-560-x-410-x-360-mm.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>distribuidor IE - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) distribuidor PL - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
@@ -3214,22 +3713,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hoja técnica EU</t>
+          <t>cajones</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PDF milwaukeetool.eu alojado en RS (no descargable: bloqueado)</t>
+          <t>CAT pag. 11 (imagen): cajon 16.3 x 12.5 in, 3 in de alto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://docs.rs-online.com/ea05/A700000009313529.pdf</t>
+          <t>https://www.milwaukeetool.com/-/media/PDFs/Sizing-Charts/PACKOUT-2023-Dimension-Catalog.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>oficial Milwaukee EU (vía RS) - no leído</t>
+          <t>fabricante (leido hoy, pagina completa)</t>
         </is>
       </c>
     </row>
@@ -3241,22 +3740,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>peso_vacio</t>
+          <t>ext</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25.8 lb (US, snippet) vs 10.04 kg (Home Depot MX) vs 10 kg (UK)</t>
+          <t>CAT pag. 11 + MLK; HDUS 16.3 x 22.2 x 14.3; HDMX 40.89 x 36.2 cm (fondo x alto)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramientas-packout-de-3-cajones-milwaukee-48-22-8443-165831</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-Modular-3-Drawer-Tool-Box-with-Metal-Reinforced-Corners-48-22-8443/315059793</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tienda - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante + distribuidor EUA</t>
         </is>
       </c>
     </row>
@@ -3268,22 +3767,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dim HD MX</t>
+          <t>ext_in</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>36.2 x 40.89 x 40.89 cm (largo/ancho/prof.) — inconsistente</t>
+          <t>16.3 L x 22.2 W x 14.3 H in</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramientas-packout-de-3-cajones-milwaukee-48-22-8443-165831</t>
+          <t>https://www.northerntool.com/products/milwaukee-packout-3-drawer-tool-box-16-3in-l-x-22-2in-w-x-14-3in-h-model-48-22-8443-103365</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
@@ -3295,191 +3794,191 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>int_in</t>
+          <t>ext_mm (UK 4932472130)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16 1/2 W x 16 D x 3.4 H in</t>
+          <t>363 x 564 x 414 mm; peso 10 kg; capacidad 22 kg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.zoro.com/milwaukee-packout-3-drawer-tool-box-48-22-8443/i/G700719735/</t>
+          <t>https://www.electricalwholesaler.ie/en/products/milwaukee-packout-3-drawer-tool-box-4932472130</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress) (atribución incierta)</t>
+          <t>(sesion anterior) distribuidor IE - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>48-22-8447</t>
+          <t>48-22-8443</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ext_in</t>
+          <t>hoja técnica EU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22.2 W x 14.3 H x 16.3 D in</t>
+          <t>PDF milwaukeetool.eu alojado en RS (no descargable: bloqueado)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.milwaukeetool.com/products/details/packout-multi-depth-3-drawer-tool-box/48-22-8447</t>
+          <t>https://docs.rs-online.com/ea05/A700000009313529.pdf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>oficial Milwaukee / tiendas - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) oficial Milwaukee EU (vía RS) - no leído</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48-22-8447</t>
+          <t>48-22-8443</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ext_cm (MX)</t>
+          <t>peso_vacio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>56.4 cm largo x 41.4 cm ancho</t>
+          <t>25.8 lb (US, snippet) vs 10.04 kg (Home Depot MX) vs 10 kg (UK)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.milwaukeetool.com/es/productos/detalles/caja-de-herramientas-de-3-cajones-de-profundidades-multiples-packout/48-22-8447</t>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramientas-packout-de-3-cajones-milwaukee-48-22-8443-165831</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress) (atribución incierta)</t>
+          <t>(sesion anterior) tienda - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>48-22-8447</t>
+          <t>48-22-8443</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>int_mm</t>
+          <t>dim HD MX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>61/61/130 x 416 x 322 mm</t>
+          <t>36.2 x 40.89 x 40.89 cm (largo/ancho/prof.) — inconsistente</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.romfordtools.com/Milwaukee-4932493190-PACKOUT-2-Plus-1-Drawer-Tool-Box/P12002</t>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramientas-packout-de-3-cajones-milwaukee-48-22-8443-165831</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>48-22-8444</t>
+          <t>48-22-8443</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ext_in</t>
+          <t>int_in</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16.3 L x 22.2 W x 14.3 H in</t>
+          <t>16 1/2 W x 16 D x 3.4 H in</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.toolnut.com/products/milwaukee-48-22-8444-packout-4-drawer-tool-box</t>
+          <t>https://www.zoro.com/milwaukee-packout-3-drawer-tool-box-48-22-8443/i/G700719735/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress) (atribución incierta)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>48-22-8444</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ext_mm (UK)</t>
+          <t>cajones</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>363 x 564 x 414 mm</t>
+          <t>MLK imagen "48-22-8447 Dimensions": 2 cajones de 2.5 in (6.35 cm); MLK imagen "48-22-8447 Dimensions": 1 cajon de 5 in (12.7 cm)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.cef.co.uk/catalogue/products/5282639-packout-4-drawer-tool-box</t>
+          <t>https://www.milwaukeetool.com/products/48-22-8447</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante (leido hoy, pagina completa)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>48-22-8444</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>int_mm</t>
+          <t>ext</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>61 x 416 x 322 mm; 11 kg/cajón</t>
+          <t>MLK; HDUS 16.10 x 22.2 x 14.3 in</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://electricalwholesaler.uk/products/milwaukee-packout-4-drawer-tool-box-48-22-8444</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-Modular-3-Drawer-Multi-Drawer-Tool-Box-with-Metal-Reinforced-Corners-and-50-lbs-Capacity-48-22-8447/326479354</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante + distribuidor EUA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>48-22-8441</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3489,132 +3988,132 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22.2 W x 16.3 L x 14.3 H in; 50 lb</t>
+          <t>22.2 W x 14.3 H x 16.3 D in</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.redtoolstore.com/products/milwaukee-48-22-8441-packout-single-drawer-tool-box-22-2-w-x-16-3-l-x-14-3-h-with-locking-bar-and-dividers</t>
+          <t>https://www.milwaukeetool.com/products/details/packout-multi-depth-3-drawer-tool-box/48-22-8447</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) oficial Milwaukee / tiendas - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>48-22-8441</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>existencia</t>
+          <t>ext_cm (MX)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>página oficial</t>
+          <t>56.4 cm largo x 41.4 cm ancho</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.milwaukeetool.com/products/details/packout-single-drawer-tool-box/48-22-8441</t>
+          <t>https://www.milwaukeetool.com/es/productos/detalles/caja-de-herramientas-de-3-cajones-de-profundidades-multiples-packout/48-22-8447</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>oficial Milwaukee - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress) (atribución incierta)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ext_in/int_in</t>
+          <t>int_mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ext 24 x 19 x 19.75 in; int 17 x 13 x 16 in; 250 lb</t>
+          <t>61/61/130 x 416 x 322 mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://toolguyd.com/milwaukee-packout-single-drawer-rolling-tool-box-48-22-8420-launch/</t>
+          <t>https://www.romfordtools.com/Milwaukee-4932493190-PACKOUT-2-Plus-1-Drawer-Tool-Box/P12002</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>blog especializado - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>peso_vacio</t>
+          <t>cajones</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>29 lb</t>
+          <t>MLK imagen "48-22-8444 Dimensions": cajon 16.3 x 12.5 in, 2.3 in (5.8 cm) de alto; respuesta de comprador en HDUS repite 2.3 x 16.3 x 12.5 in tomado de la misma imagen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/48-22-8420-Milwaukee-Rolling-Drawer-Collapsible/dp/B0HBNWRZ3Y</t>
+          <t>https://www.milwaukeetool.com/products/48-22-8444</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amazon US (vendedor tercero, título) - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante (leido hoy, pagina completa)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>ext</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PACKOUT Rolling Drawer Tool Box</t>
+          <t>MLK Length 16.3 / Width 22.2 / Height 14.3 in; HDUS 16.10 x 22.2 x 14.3 in (5 mm menos de fondo)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.milwaukeetool.com/products/details/packout-rolling-drawer-tool-box/48-22-8420</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-22-in-Modular-4-Drawer-Tool-Box-with-Metal-Reinforced-Corners-and-50-lbs-Capacity-48-22-8444/326480385</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>oficial - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante + distribuidor EUA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>48-22-8426</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3624,233 +4123,789 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22.1 x 18.6 x 25.6 in; interior 19.1 x 14.6 x 13.9 in; 250 lb; IP65; ruedas 9 in</t>
+          <t>16.3 L x 22.2 W x 14.3 H in</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://merrimacindustrial.com/milwaukee-packouttm-impact-resistant-polymer-waterproof-rolling-tool-box-22-1-x-18-6-x-25-6-in-250-lb</t>
+          <t>https://www.toolnut.com/products/milwaukee-48-22-8444-packout-4-drawer-tool-box</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>distribuidor US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>48-22-8426</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ext_cm (MX)</t>
+          <t>ext_mm (UK)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>67 x 49 x 47.24 cm; 113.39 kg</t>
+          <t>363 x 564 x 414 mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramienta-packout-con-llantas-67-x-49-x-4724-cm-milwaukee-48-22-8426-139086</t>
+          <t>https://www.cef.co.uk/catalogue/products/5282639-packout-4-drawer-tool-box</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>48-22-8410</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ext_in</t>
+          <t>int_mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24.4 L x 18.9 W x 7.6 H in; ruedas 4 in; 250 lb</t>
+          <t>61 x 416 x 322 mm; 11 kg/cajón</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.rshughes.com/p/Milwaukee-PACKOUT-48-22-8410-Dolly-250-Lb-Capacity-Impact-Resistant-Polymers-52408/045242_52408/</t>
+          <t>https://electricalwholesaler.uk/products/milwaukee-packout-4-drawer-tool-box-48-22-8444</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>distribuidor US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) distribuidor UK - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>48-22-8415</t>
+          <t>48-22-8441</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ext_in</t>
+          <t>cajones</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21.13 W x 12 D x 48 H in; 400 lb; ruedas 10 in anti-ponchadura</t>
+          <t>MLK imagen "48-22-8441 Dimensions 101": cajon 16.5 x 13 in (41.9 x 33 cm), 10.25 in (26 cm)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.outdoorsupplyhardware.com/2800986/product/milwaukee-48-22-8415</t>
+          <t>https://www.milwaukeetool.com/products/48-22-8441</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>distribuidor US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante (leido hoy, pagina completa)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>48-22-8440</t>
+          <t>48-22-8441</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ext/int</t>
+          <t>ext</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ext 18.6 x 15.4 x 9.9 in; int 16 x 13 x 9 in; 1872 in3; 50 lb</t>
+          <t>MLK imagen: 22.2 x 16.3 x 14 in; MLK especificaciones Height 14.3; HDUS 22 x 22.5 x 14.5 in</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-18-6-in-Tool-Storage-Crate-Bin-with-Carrying-Handles-and-50-lbs-Weight-Capacity-48-22-8440/311569700</t>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-Single-Drawer-Tool-Box-48-22-8441/342729532</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante + distribuidor EUA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>48-22-8450</t>
+          <t>48-22-8441</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ext_cm (MX)</t>
+          <t>ext_in</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15.01 x 38 x 52.9 cm; 34.01 kg; 75 lb</t>
+          <t>22.2 W x 16.3 L x 14.3 H in; 50 lb</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-almacenamiento-packout-con-inserto-1501-x-38-x-529-cm-milwaukee-48-22-8450-139212</t>
+          <t>https://www.redtoolstore.com/products/milwaukee-48-22-8441-packout-single-drawer-tool-box-22-2-w-x-16-3-l-x-14-3-h-with-locking-bar-and-dividers</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>48-22-8450</t>
+          <t>48-22-8441</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ext_in (US)</t>
+          <t>existencia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20.59 x 14.84 x 5.91 in; 5.69 lb</t>
+          <t>página oficial</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Milwaukee-MLW48228450-Packout-Tool-Insert/dp/B07LH3BMZ4</t>
+          <t>https://www.milwaukeetool.com/products/details/packout-single-drawer-tool-box/48-22-8441</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>(sesion anterior) oficial Milwaukee - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>48-22-8450</t>
+          <t>48-22-8420</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ext_in (alterno)</t>
+          <t>cajones</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20.7 W x 15.2 L x 6.2 H in</t>
+          <t>MLK imagen "48-22-8420 Dimensions 101": 13 in de ancho de cajon y 16 in de alto; el tercer lado (432 mm) sigue siendo fragmento de buscador</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.toolnut.com/products/milwaukee-48-22-8450-packout-tool-case-with-customizable-insert</t>
+          <t>https://www.milwaukeetool.com/products/48-22-8420</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+          <t>fabricante (leido hoy, pagina completa)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ext</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MLK imagen: 24 x 19 x 19.75 in; MLK especificaciones 24 x 19 x 20 in; HDUS 23.9 x 19.49 x 19.82 in</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-19-in-Rolling-Drawer-Tool-Box-48-22-8420/334615696</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>fabricante + distribuidor EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ext_in/int_in</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ext 24 x 19 x 19.75 in; int 17 x 13 x 16 in; 250 lb</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://toolguyd.com/milwaukee-packout-single-drawer-rolling-tool-box-48-22-8420-launch/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>(sesion anterior) blog especializado - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>peso_vacio</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>29 lb</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/48-22-8420-Milwaukee-Rolling-Drawer-Collapsible/dp/B0HBNWRZ3Y</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>(sesion anterior) Amazon US (vendedor tercero, título) - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>oficial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PACKOUT Rolling Drawer Tool Box</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.milwaukeetool.com/products/details/packout-rolling-drawer-tool-box/48-22-8420</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>(sesion anterior) oficial - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>48-22-8426</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ext_in</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22.1 x 18.6 x 25.6 in; interior 19.1 x 14.6 x 13.9 in; 250 lb; IP65; ruedas 9 in</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://merrimacindustrial.com/milwaukee-packouttm-impact-resistant-polymer-waterproof-rolling-tool-box-22-1-x-18-6-x-25-6-in-250-lb</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>distribuidor US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>48-22-8426</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ext_cm (MX)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>67 x 49 x 47.24 cm; 113.39 kg</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-herramienta-packout-con-llantas-67-x-49-x-4724-cm-milwaukee-48-22-8426-139086</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>48-22-8410</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ext_in</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>24.4 L x 18.9 W x 7.6 H in; ruedas 4 in; 250 lb</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.rshughes.com/p/Milwaukee-PACKOUT-48-22-8410-Dolly-250-Lb-Capacity-Impact-Resistant-Polymers-52408/045242_52408/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>distribuidor US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>48-22-8415</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ext_in</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>21.13 W x 12 D x 48 H in; 400 lb; ruedas 10 in anti-ponchadura</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.outdoorsupplyhardware.com/2800986/product/milwaukee-48-22-8415</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>distribuidor US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>48-22-8440</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ext/int</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ext 18.6 x 15.4 x 9.9 in; int 16 x 13 x 9 in; 1872 in3; 50 lb</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.homedepot.com/p/Milwaukee-PACKOUT-18-6-in-Tool-Storage-Crate-Bin-with-Carrying-Handles-and-50-lbs-Weight-Capacity-48-22-8440/311569700</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>48-22-8450</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ext_cm (MX)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>15.01 x 38 x 52.9 cm; 34.01 kg; 75 lb</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.homedepot.com.mx/p/milwaukee-caja-de-almacenamiento-packout-con-inserto-1501-x-38-x-529-cm-milwaukee-48-22-8450-139212</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>tienda MX - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>48-22-8450</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ext_in (US)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>20.59 x 14.84 x 5.91 in; 5.69 lb</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/Milwaukee-MLW48228450-Packout-Tool-Insert/dp/B07LH3BMZ4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>48-22-8450</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ext_in (alterno)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20.7 W x 15.2 L x 6.2 H in</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.toolnut.com/products/milwaukee-48-22-8450-packout-tool-case-with-customizable-insert</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>tienda US - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>48-22-8445</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>ext_in</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>19.5 x 14.7 x 14.5 in</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>https://www.homedepot.com/p/Milwaukee-Packout-19-5-in-W-x-14-7-in-H-x-14-5-in-D-Cabinet-in-Red-1-Piece-48-22-8445/320324795</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>tienda US (título) - snippet_buscador (WebSearch; página NO abierta: host bloqueado por egress)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>modelo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cajones antes (n x ancho x fondo x alto mm)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>cajones ahora</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>barra para candado</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2 x 414x318x127</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2 x 414x318x127</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3 x 414x318x76</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3 x 414x318x76</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Discrepancia 76 contra 86 mm: el fabricante da 3 in = 76 mm. Los 86 mm de la ficha de EUA no se sostienen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2 x 416x322x61 | 1 x 416x322x130</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2 x 414x318x63 | 1 x 414x318x127</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Discrepancia 8442 contra 8447: la division 61 + 61 + 130 que la ficha UK atribuia al 8442 es la del 8447 (oficial: 63.5 + 63.5 + 127). El 8442 son 2 cajones de 127.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4 x 416x322x61</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4 x 414x318x58</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>El cajon es de 58 mm, NO de 61 mm (fragmento UK de la sesion anterior). La imagen oficial rotula 22.2 in como "54.4 cm": error de la imagen, 22.2 in = 56.4 cm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>48-22-8441</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1 x NonexNonexNone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1 x 419x330x260</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1 x 432x330x406</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1 x 432x330x406</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Incluye 2 divisores grandes, 6 divisores y una bandeja interior (MLK "Includes"). Peso: MLK 29 lb, HDUS 36 lb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(todos)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fuente: ficha del fabricante leida el 2026-09-28 (la red ya abre milwaukeetool.com). Ninguna cota tiene medicion fisica: nivel maximo D2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>nuevos 2025-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sitemap de milwaukeetool.com: los unicos PACKOUT de cajones son 8441, 8442, 8443, 8444, 8447 y 8420. No hay modelo nuevo de cajones. Si hay espuma para cajones 48-22-8452 (8442/8443) y 48-22-8453 (8442/8443/8444/8447, 2 piezas, 3.6 in).</t>
         </is>
       </c>
     </row>
